--- a/Team-Data/2014-15/4-9-2014-15.xlsx
+++ b/Team-Data/2014-15/4-9-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -772,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1115,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>16</v>
@@ -1136,7 +1203,7 @@
         <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
         <v>19</v>
@@ -1157,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L6" t="n">
         <v>7.8</v>
@@ -1419,25 +1486,25 @@
         <v>22.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O6" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S6" t="n">
         <v>33.9</v>
       </c>
       <c r="T6" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="U6" t="n">
         <v>21.8</v>
@@ -1446,31 +1513,31 @@
         <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
         <v>5.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA6" t="n">
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,16 +1546,16 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
@@ -1530,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1679,16 +1746,16 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1700,7 +1767,7 @@
         <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>14</v>
@@ -1718,7 +1785,7 @@
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
         <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>0.603</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,7 +1838,7 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
@@ -1783,7 +1850,7 @@
         <v>25.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O8" t="n">
         <v>16.7</v>
@@ -1792,28 +1859,28 @@
         <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1831,7 +1898,7 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1861,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1870,16 +1937,16 @@
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,7 +2092,7 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2046,7 +2113,7 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2249,7 +2316,7 @@
         <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>16</v>
@@ -2264,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2320,7 +2387,7 @@
         <v>87.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L11" t="n">
         <v>10.7</v>
@@ -2332,13 +2399,13 @@
         <v>0.396</v>
       </c>
       <c r="O11" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
@@ -2362,13 +2429,13 @@
         <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB11" t="n">
         <v>109.6</v>
@@ -2377,7 +2444,7 @@
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2419,7 +2486,7 @@
         <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.442</v>
@@ -2511,34 +2578,34 @@
         <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
@@ -2547,28 +2614,28 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2580,7 +2647,7 @@
         <v>12</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,16 +2659,16 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
@@ -2628,13 +2695,13 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>20</v>
@@ -2753,7 +2820,7 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2771,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>15</v>
@@ -2780,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.26</v>
+        <v>0.256</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
         <v>20.8</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3150,13 +3217,13 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" t="n">
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.443</v>
+        <v>0.449</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,34 +3476,34 @@
         <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L17" t="n">
         <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N17" t="n">
         <v>0.335</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0.745</v>
       </c>
       <c r="R17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T17" t="n">
         <v>38.8</v>
@@ -3448,40 +3515,40 @@
         <v>14.9</v>
       </c>
       <c r="W17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3502,10 +3569,10 @@
         <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3523,16 +3590,16 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>17</v>
@@ -3672,7 +3739,7 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3699,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>0.532</v>
+        <v>0.538</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
         <v>0.457</v>
@@ -3967,37 +4034,37 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.759</v>
+        <v>0.754</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,25 +4073,25 @@
         <v>18.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -4033,10 +4100,10 @@
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,10 +4118,10 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4069,13 +4136,13 @@
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -4483,70 +4550,70 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
         <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P23" t="n">
         <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>20.9</v>
@@ -4555,13 +4622,13 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,19 +4646,19 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4603,19 +4670,19 @@
         <v>24</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4776,16 +4843,16 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI25" t="n">
         <v>5</v>
@@ -4961,7 +5028,7 @@
         <v>20</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.646</v>
+        <v>0.654</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J26" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
         <v>27.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O26" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5077,10 +5144,10 @@
         <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5098,34 +5165,34 @@
         <v>18.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB26" t="n">
         <v>103</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,25 +5478,25 @@
         <v>39.1</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O28" t="n">
         <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.779</v>
@@ -5441,13 +5508,13 @@
         <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W28" t="n">
         <v>8.1</v>
@@ -5465,22 +5532,22 @@
         <v>19.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC28" t="n">
         <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5501,19 +5568,19 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5525,7 +5592,7 @@
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>10</v>
@@ -5534,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
         <v>11</v>
@@ -5674,7 +5741,7 @@
         <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5701,10 +5768,10 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
@@ -5883,7 +5950,7 @@
         <v>19</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>30</v>
@@ -5895,7 +5962,7 @@
         <v>17</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5904,7 +5971,7 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6050,7 +6117,7 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>22</v>
@@ -6083,7 +6150,7 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2014-15</t>
+          <t>2015-04-09</t>
         </is>
       </c>
     </row>
